--- a/data/trans_orig/P5707-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5707-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>470095</t>
+          <t>466276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>529777</t>
+          <t>531057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590633</t>
+          <t>590553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>661832</t>
+          <t>660866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1079706</t>
+          <t>1079020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1174127</t>
+          <t>1173697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266355</t>
+          <t>269508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327469</t>
+          <t>324717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334944</t>
+          <t>333702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>402381</t>
+          <t>398973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>621754</t>
+          <t>619385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705364</t>
+          <t>705967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152303</t>
+          <t>151535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200893</t>
+          <t>199965</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204681</t>
+          <t>206020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260137</t>
+          <t>258757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>372238</t>
+          <t>370236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>445449</t>
+          <t>445808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64480</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>62205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97766</t>
+          <t>96193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107006</t>
+          <t>104882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149814</t>
+          <t>150738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>969400</t>
+          <t>972166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1052498</t>
+          <t>1056282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>907992</t>
+          <t>910125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>985929</t>
+          <t>989888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1903505</t>
+          <t>1905133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2013165</t>
+          <t>2022332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433151</t>
+          <t>433523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507803</t>
+          <t>506249</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>386080</t>
+          <t>385012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456748</t>
+          <t>457602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>841916</t>
+          <t>839796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>945979</t>
+          <t>941561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151729</t>
+          <t>152431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200259</t>
+          <t>201318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148963</t>
+          <t>144202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196836</t>
+          <t>196544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>314547</t>
+          <t>315287</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386467</t>
+          <t>385667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18365</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40711</t>
+          <t>39998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29792</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>53592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>89683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321262</t>
+          <t>321733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>367104</t>
+          <t>367302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>272995</t>
+          <t>276120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317575</t>
+          <t>316949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607266</t>
+          <t>607485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>670118</t>
+          <t>673018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132272</t>
+          <t>132421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174292</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102255</t>
+          <t>103447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142265</t>
+          <t>140609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244345</t>
+          <t>246264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303483</t>
+          <t>304878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28477</t>
+          <t>28281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58336</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67659</t>
+          <t>68622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42332</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5223</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4684</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1798989</t>
+          <t>1797343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1913151</t>
+          <t>1911884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1812354</t>
+          <t>1808213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1930201</t>
+          <t>1924366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3648158</t>
+          <t>3644789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3813011</t>
+          <t>3805966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>870477</t>
+          <t>868778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>976071</t>
+          <t>969670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>857747</t>
+          <t>858341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>960037</t>
+          <t>961824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1761809</t>
+          <t>1759734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1902616</t>
+          <t>1906674</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357350</t>
+          <t>353530</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>429758</t>
+          <t>428646</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>410226</t>
+          <t>407229</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>489659</t>
+          <t>488282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>785062</t>
+          <t>783576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>893801</t>
+          <t>887976</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73200</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>110334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111511</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159849</t>
+          <t>157598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192374</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>255986</t>
+          <t>258191</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>491618</t>
+          <t>496090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>553998</t>
+          <t>556556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>675537</t>
+          <t>673700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>753622</t>
+          <t>750973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1187536</t>
+          <t>1192979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1289441</t>
+          <t>1286148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250441</t>
+          <t>247375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308452</t>
+          <t>304318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>371565</t>
+          <t>375507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444707</t>
+          <t>443536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644318</t>
+          <t>640240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734189</t>
+          <t>726731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108170</t>
+          <t>108293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152164</t>
+          <t>152322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133963</t>
+          <t>133757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179831</t>
+          <t>181857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251648</t>
+          <t>254547</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>320396</t>
+          <t>318124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42114</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>54240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>53219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86714</t>
+          <t>86281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,82 +4159,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8870</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25532</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15836</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9112</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>24417</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>25201</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>15763</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>37589</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>25201</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>15073</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>37312</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1178889</t>
+          <t>1177385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1266758</t>
+          <t>1263214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1007772</t>
+          <t>1004684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1092496</t>
+          <t>1093688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2214949</t>
+          <t>2217949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2334153</t>
+          <t>2336502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462450</t>
+          <t>465281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542113</t>
+          <t>546267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462087</t>
+          <t>459348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537797</t>
+          <t>537795</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947796</t>
+          <t>941172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1056948</t>
+          <t>1054865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>167035</t>
+          <t>166442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221349</t>
+          <t>221522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135768</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183527</t>
+          <t>184485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>312618</t>
+          <t>314068</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>389112</t>
+          <t>386871</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>56245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89633</t>
+          <t>91622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27719</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35264</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>305930</t>
+          <t>304839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>350859</t>
+          <t>351386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294645</t>
+          <t>297265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>339482</t>
+          <t>338504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>618896</t>
+          <t>616761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>676698</t>
+          <t>675758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89266</t>
+          <t>88832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129268</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86397</t>
+          <t>85553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125248</t>
+          <t>122438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184125</t>
+          <t>184241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238604</t>
+          <t>236825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48576</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48101</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>85099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,62 +5543,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2016629</t>
+          <t>2017328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2132379</t>
+          <t>2139921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2025806</t>
+          <t>2022142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2141845</t>
+          <t>2141993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4070593</t>
+          <t>4074895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4243726</t>
+          <t>4259189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>835412</t>
+          <t>827487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>942430</t>
+          <t>932527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>948757</t>
+          <t>952262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1063057</t>
+          <t>1068809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1823626</t>
+          <t>1812022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1976456</t>
+          <t>1977457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>320124</t>
+          <t>320228</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>396362</t>
+          <t>393608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311725</t>
+          <t>313086</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>383323</t>
+          <t>384787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>652238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>755821</t>
+          <t>755674</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57376</t>
+          <t>58150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>92174</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>60864</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97751</t>
+          <t>97247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128533</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179195</t>
+          <t>180656</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67961</t>
+          <t>66923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>324022</t>
+          <t>317439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>378598</t>
+          <t>374515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407731</t>
+          <t>403490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>474130</t>
+          <t>471590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>745768</t>
+          <t>741044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>828089</t>
+          <t>825481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224907</t>
+          <t>225936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274485</t>
+          <t>278424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308457</t>
+          <t>309327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>370947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551951</t>
+          <t>550170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631032</t>
+          <t>631888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108450</t>
+          <t>106410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148331</t>
+          <t>148743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129746</t>
+          <t>129168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179820</t>
+          <t>176497</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>250557</t>
+          <t>248541</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310255</t>
+          <t>310704</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63609</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98923</t>
+          <t>100456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>972686</t>
+          <t>972231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1067613</t>
+          <t>1061423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>959719</t>
+          <t>960143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1046916</t>
+          <t>1049578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1957985</t>
+          <t>1957817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2088458</t>
+          <t>2082827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644542</t>
+          <t>641272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729093</t>
+          <t>729060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647714</t>
+          <t>645009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>729858</t>
+          <t>726836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315106</t>
+          <t>1314359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1437566</t>
+          <t>1434096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275986</t>
+          <t>278056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344449</t>
+          <t>345961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228096</t>
+          <t>226296</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>288505</t>
+          <t>291481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>530210</t>
+          <t>525344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619713</t>
+          <t>619792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57420</t>
+          <t>55236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82950</t>
+          <t>84140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39818</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281547</t>
+          <t>280801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>329345</t>
+          <t>328156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316033</t>
+          <t>316605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>361293</t>
+          <t>361222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>610295</t>
+          <t>611578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>676080</t>
+          <t>679417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162455</t>
+          <t>162061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207185</t>
+          <t>206277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125455</t>
+          <t>124349</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168778</t>
+          <t>163929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>298541</t>
+          <t>297138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359500</t>
+          <t>359784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71642</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39781</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>68589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>87665</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129182</t>
+          <t>127487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,62 +8502,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4971</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1607781</t>
+          <t>1615878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1726915</t>
+          <t>1734142</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1725148</t>
+          <t>1724015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1844535</t>
+          <t>1839384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3360089</t>
+          <t>3362704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3531704</t>
+          <t>3534547</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1065291</t>
+          <t>1064926</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1175661</t>
+          <t>1178865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1119585</t>
+          <t>1114141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1234480</t>
+          <t>1224791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2217704</t>
+          <t>2209955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2368861</t>
+          <t>2373808</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>455263</t>
+          <t>454002</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>533153</t>
+          <t>535854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>422102</t>
+          <t>423774</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>504646</t>
+          <t>507855</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>896638</t>
+          <t>903886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1016205</t>
+          <t>1021691</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53206</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85092</t>
+          <t>85269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69598</t>
+          <t>69015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109306</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131995</t>
+          <t>130674</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185020</t>
+          <t>181817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>31435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>55925</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas personales y familiares en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232134</t>
+          <t>232952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273827</t>
+          <t>276868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321265</t>
+          <t>323879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>365885</t>
+          <t>367717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>566218</t>
+          <t>570108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>629225</t>
+          <t>629768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127398</t>
+          <t>128310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164754</t>
+          <t>165772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218244</t>
+          <t>216622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257633</t>
+          <t>256240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355169</t>
+          <t>356151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407617</t>
+          <t>409936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62696</t>
+          <t>61916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91824</t>
+          <t>91100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93577</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>161393</t>
+          <t>160853</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201473</t>
+          <t>201442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58005</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62248</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>86329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20976</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1262268</t>
+          <t>1263171</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1649205</t>
+          <t>1668639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>848719</t>
+          <t>843088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1340762</t>
+          <t>1331782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2244967</t>
+          <t>2236077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2844139</t>
+          <t>2879575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493242</t>
+          <t>483088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>803399</t>
+          <t>802617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467010</t>
+          <t>469782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>735756</t>
+          <t>734302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1102065</t>
+          <t>1092530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1509818</t>
+          <t>1499373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97191</t>
+          <t>95002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167919</t>
+          <t>167647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96165</t>
+          <t>94852</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156680</t>
+          <t>158767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>213919</t>
+          <t>214116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>309904</t>
+          <t>312643</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63563</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53619</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>843138</t>
+          <t>816464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96935</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1136448</t>
+          <t>1009431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>42986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>397158</t>
+          <t>395643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445338</t>
+          <t>447923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436575</t>
+          <t>436856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>478337</t>
+          <t>477546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>844946</t>
+          <t>848388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>909647</t>
+          <t>914874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154748</t>
+          <t>152877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200716</t>
+          <t>201969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150657</t>
+          <t>149784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189706</t>
+          <t>188426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316733</t>
+          <t>315855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376857</t>
+          <t>374246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>42717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>40113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69588</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9855</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1940342</t>
+          <t>1944804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2376665</t>
+          <t>2391931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1584726</t>
+          <t>1614938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2141988</t>
+          <t>2131389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3720870</t>
+          <t>3726486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4351977</t>
+          <t>4349697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>807781</t>
+          <t>780360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1128298</t>
+          <t>1119048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>850043</t>
+          <t>831364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1139151</t>
+          <t>1139709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1805820</t>
+          <t>1767863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2226497</t>
+          <t>2211603</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191835</t>
+          <t>185850</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281060</t>
+          <t>277877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>211347</t>
+          <t>212886</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289065</t>
+          <t>289061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>433686</t>
+          <t>425593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>553377</t>
+          <t>544610</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>63662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107421</t>
+          <t>108011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>106310</t>
+          <t>107846</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>954823</t>
+          <t>939873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187558</t>
+          <t>188971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1127385</t>
+          <t>982698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36361</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>49349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5707-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5707-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>466276</t>
+          <t>469608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>531057</t>
+          <t>531136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>590553</t>
+          <t>587871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>660866</t>
+          <t>659670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1079020</t>
+          <t>1074351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1173697</t>
+          <t>1174120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269508</t>
+          <t>270718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>324717</t>
+          <t>326462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333702</t>
+          <t>334169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398973</t>
+          <t>398733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>619385</t>
+          <t>621048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>705967</t>
+          <t>706886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151535</t>
+          <t>153288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>199965</t>
+          <t>201139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206020</t>
+          <t>206678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258757</t>
+          <t>262498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>370236</t>
+          <t>369600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>445808</t>
+          <t>447490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>62139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>97716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104882</t>
+          <t>107725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150738</t>
+          <t>149081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>972166</t>
+          <t>973019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1056282</t>
+          <t>1058259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>910125</t>
+          <t>907586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>989888</t>
+          <t>987160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1905133</t>
+          <t>1901867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2022332</t>
+          <t>2018983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433523</t>
+          <t>431209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506249</t>
+          <t>505966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>385012</t>
+          <t>386924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457602</t>
+          <t>455580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>839796</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>941561</t>
+          <t>949609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152431</t>
+          <t>151547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201318</t>
+          <t>200411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144202</t>
+          <t>149478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196544</t>
+          <t>199709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>315287</t>
+          <t>317160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385667</t>
+          <t>384194</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>57887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53592</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89683</t>
+          <t>88873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321733</t>
+          <t>321392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>367302</t>
+          <t>369037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>276120</t>
+          <t>274838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316949</t>
+          <t>318691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607485</t>
+          <t>609548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>673018</t>
+          <t>672669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132421</t>
+          <t>132326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>174759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103447</t>
+          <t>101767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140609</t>
+          <t>139873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246264</t>
+          <t>244301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>304878</t>
+          <t>302894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28281</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32746</t>
+          <t>33325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>59034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68622</t>
+          <t>67291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105367</t>
+          <t>103303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>43100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1797343</t>
+          <t>1800972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1911884</t>
+          <t>1914104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1808213</t>
+          <t>1810851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1924366</t>
+          <t>1927791</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3644789</t>
+          <t>3648416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3805966</t>
+          <t>3807834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>868778</t>
+          <t>871347</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>969670</t>
+          <t>979352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>858341</t>
+          <t>859524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>961824</t>
+          <t>964998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1759734</t>
+          <t>1750587</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1906674</t>
+          <t>1895368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>353530</t>
+          <t>355661</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>428646</t>
+          <t>428934</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>407229</t>
+          <t>409883</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>488282</t>
+          <t>490619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>783576</t>
+          <t>788210</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>887976</t>
+          <t>899801</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110334</t>
+          <t>110628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>112316</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157598</t>
+          <t>157358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>198659</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258191</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25466</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25999</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>45742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>496090</t>
+          <t>491436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>556556</t>
+          <t>555973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>673700</t>
+          <t>676034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>750973</t>
+          <t>749721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1192979</t>
+          <t>1186430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1286148</t>
+          <t>1286911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247375</t>
+          <t>247483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304318</t>
+          <t>308021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375507</t>
+          <t>378011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>443536</t>
+          <t>445340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640240</t>
+          <t>638783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726731</t>
+          <t>727982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108293</t>
+          <t>109782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152322</t>
+          <t>153644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>134603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>181857</t>
+          <t>183241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254547</t>
+          <t>253561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>318124</t>
+          <t>323355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>41401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54240</t>
+          <t>54218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53219</t>
+          <t>53762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86281</t>
+          <t>87884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1177385</t>
+          <t>1173619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1263214</t>
+          <t>1264674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1004684</t>
+          <t>1008054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1093688</t>
+          <t>1095369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2217949</t>
+          <t>2214638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2336502</t>
+          <t>2337188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465281</t>
+          <t>460399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546267</t>
+          <t>541369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459348</t>
+          <t>456606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537795</t>
+          <t>538308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>941172</t>
+          <t>940876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1054865</t>
+          <t>1056701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166442</t>
+          <t>167359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221522</t>
+          <t>220596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>132792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184485</t>
+          <t>183603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>314068</t>
+          <t>312971</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386871</t>
+          <t>389389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50620</t>
+          <t>48568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>91148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>35543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304839</t>
+          <t>304689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>351386</t>
+          <t>349905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297265</t>
+          <t>298184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>338504</t>
+          <t>336889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>616761</t>
+          <t>616446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>675758</t>
+          <t>678141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88832</t>
+          <t>90922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128500</t>
+          <t>129718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85553</t>
+          <t>85939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122438</t>
+          <t>122292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184241</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236825</t>
+          <t>239750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47759</t>
+          <t>46385</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48679</t>
+          <t>49497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>85945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2017328</t>
+          <t>2011168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2139921</t>
+          <t>2134972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2022142</t>
+          <t>2020899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2141993</t>
+          <t>2143282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4074895</t>
+          <t>4074114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4259189</t>
+          <t>4241760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>827487</t>
+          <t>834698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>932527</t>
+          <t>941081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>952262</t>
+          <t>950722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1068809</t>
+          <t>1064590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1812022</t>
+          <t>1823215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1977457</t>
+          <t>1975480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>320228</t>
+          <t>319071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>393608</t>
+          <t>393810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>313086</t>
+          <t>310621</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>384787</t>
+          <t>387584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>652238</t>
+          <t>651678</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>755674</t>
+          <t>752810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58150</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92174</t>
+          <t>93482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97247</t>
+          <t>97591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129843</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180656</t>
+          <t>180341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>29359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66923</t>
+          <t>65973</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317439</t>
+          <t>320443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374515</t>
+          <t>372174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>403490</t>
+          <t>403473</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>471590</t>
+          <t>470506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>741044</t>
+          <t>745289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>825481</t>
+          <t>830385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225936</t>
+          <t>226901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278424</t>
+          <t>278822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309327</t>
+          <t>308636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370947</t>
+          <t>373157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550170</t>
+          <t>548417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631888</t>
+          <t>631235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>108441</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148743</t>
+          <t>149095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129168</t>
+          <t>129520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176497</t>
+          <t>178859</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>248541</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310704</t>
+          <t>311065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>38467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>68095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>60799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100456</t>
+          <t>99536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>973934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1061423</t>
+          <t>1063597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>960143</t>
+          <t>962635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1049578</t>
+          <t>1050115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1957817</t>
+          <t>1959103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2082827</t>
+          <t>2084565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641272</t>
+          <t>646036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729060</t>
+          <t>731880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645009</t>
+          <t>647966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>726836</t>
+          <t>730771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314359</t>
+          <t>1315641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1434096</t>
+          <t>1434036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278056</t>
+          <t>276584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345961</t>
+          <t>343000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>226296</t>
+          <t>227523</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>291481</t>
+          <t>290795</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>525344</t>
+          <t>529395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619792</t>
+          <t>618597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55236</t>
+          <t>55865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34799</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84140</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>280801</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328156</t>
+          <t>331223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316605</t>
+          <t>316452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>361222</t>
+          <t>362669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>611578</t>
+          <t>611543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>679417</t>
+          <t>679341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162061</t>
+          <t>159840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206277</t>
+          <t>207823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124349</t>
+          <t>126087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163929</t>
+          <t>167754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297138</t>
+          <t>299474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359784</t>
+          <t>360958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41810</t>
+          <t>41377</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41034</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68589</t>
+          <t>68938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>89113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127487</t>
+          <t>130118</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1615878</t>
+          <t>1612987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1734142</t>
+          <t>1729864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1724015</t>
+          <t>1721621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1839384</t>
+          <t>1841850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3362704</t>
+          <t>3370350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3534547</t>
+          <t>3529587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1064926</t>
+          <t>1065278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1178865</t>
+          <t>1177898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1114141</t>
+          <t>1113041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1224791</t>
+          <t>1231295</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2209955</t>
+          <t>2216463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2373808</t>
+          <t>2369911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>454002</t>
+          <t>453966</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>535854</t>
+          <t>535232</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423774</t>
+          <t>421307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>507855</t>
+          <t>506218</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>903886</t>
+          <t>899716</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1021691</t>
+          <t>1016545</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85269</t>
+          <t>87734</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69015</t>
+          <t>67253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103894</t>
+          <t>106338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130674</t>
+          <t>131044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181817</t>
+          <t>184882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55925</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>254068</t>
+          <t>280860</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232952</t>
+          <t>257109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>276868</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>343658</t>
+          <t>365001</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>323879</t>
+          <t>342655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>367717</t>
+          <t>387299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>597726</t>
+          <t>645862</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>570108</t>
+          <t>616799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>629768</t>
+          <t>682128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>145878</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128310</t>
+          <t>142367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165772</t>
+          <t>182770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236665</t>
+          <t>262402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216622</t>
+          <t>241617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256240</t>
+          <t>284210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>382543</t>
+          <t>423821</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356151</t>
+          <t>394330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409936</t>
+          <t>455250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>91681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61916</t>
+          <t>76944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91100</t>
+          <t>112280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105241</t>
+          <t>116368</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92113</t>
+          <t>101908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>130747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>180815</t>
+          <t>208050</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>160853</t>
+          <t>184376</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201442</t>
+          <t>232191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58502</t>
+          <t>64156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72747</t>
+          <t>81956</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61494</t>
+          <t>68163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86329</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,27 +10127,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36817</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>512938</t>
+          <t>576412</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>512938</t>
+          <t>576412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512938</t>
+          <t>576412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>748855</t>
+          <t>814902</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>748855</t>
+          <t>814902</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>748855</t>
+          <t>814902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1261793</t>
+          <t>1391315</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1261793</t>
+          <t>1391315</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1261793</t>
+          <t>1391315</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1391481</t>
+          <t>1214096</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1263171</t>
+          <t>1162811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1668639</t>
+          <t>1266236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1187670</t>
+          <t>1208695</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>843088</t>
+          <t>1164398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1331782</t>
+          <t>1249889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2579151</t>
+          <t>2422791</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2354361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2879575</t>
+          <t>2491479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>700970</t>
+          <t>780963</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483088</t>
+          <t>723634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>802617</t>
+          <t>826873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>643566</t>
+          <t>724350</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469782</t>
+          <t>688660</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>734302</t>
+          <t>770857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1344536</t>
+          <t>1505313</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1092530</t>
+          <t>1443002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1499373</t>
+          <t>1570267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>137288</t>
+          <t>157927</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95002</t>
+          <t>133844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167647</t>
+          <t>188351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>130525</t>
+          <t>151726</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94852</t>
+          <t>130317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158767</t>
+          <t>174637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>267813</t>
+          <t>309654</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>214116</t>
+          <t>276314</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>312643</t>
+          <t>347540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>55719</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>41554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>73801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52715</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>816464</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302804</t>
+          <t>119278</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94708</t>
+          <t>99039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1009431</t>
+          <t>140057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27738</t>
+          <t>37032</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2286636</t>
+          <t>2225090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2286636</t>
+          <t>2225090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2286636</t>
+          <t>2225090</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235406</t>
+          <t>2168978</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235406</t>
+          <t>2168978</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235406</t>
+          <t>2168978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4522042</t>
+          <t>4394068</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4522042</t>
+          <t>4394068</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4522042</t>
+          <t>4394068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>422293</t>
+          <t>458840</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>395643</t>
+          <t>432931</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>447923</t>
+          <t>486124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>457873</t>
+          <t>505221</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>436856</t>
+          <t>483008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>477546</t>
+          <t>526445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>880166</t>
+          <t>964061</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>848388</t>
+          <t>928243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>914874</t>
+          <t>999154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177329</t>
+          <t>198241</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152877</t>
+          <t>173799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201969</t>
+          <t>222160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>168643</t>
+          <t>191003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149784</t>
+          <t>170690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188426</t>
+          <t>212478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>345973</t>
+          <t>389243</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315855</t>
+          <t>354010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374246</t>
+          <t>422100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>34310</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,17 +11230,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,27 +11265,27 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>58596</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>44193</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>76103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,22 +11456,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645299</t>
+          <t>710242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645299</t>
+          <t>710242</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645299</t>
+          <t>710242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305603</t>
+          <t>1444451</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305603</t>
+          <t>1444451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305603</t>
+          <t>1444451</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2067841</t>
+          <t>1953798</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1944804</t>
+          <t>1894360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2391931</t>
+          <t>2020396</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1989200</t>
+          <t>2078917</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1614938</t>
+          <t>2024684</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2131389</t>
+          <t>2132770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4057042</t>
+          <t>4032714</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3726486</t>
+          <t>3952330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4349697</t>
+          <t>4120146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1024177</t>
+          <t>1140622</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>780360</t>
+          <t>1080894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1119048</t>
+          <t>1200885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1048874</t>
+          <t>1177755</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>831364</t>
+          <t>1127977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1139709</t>
+          <t>1226900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2073051</t>
+          <t>2318377</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1767863</t>
+          <t>2243461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2211603</t>
+          <t>2396229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>242810</t>
+          <t>283919</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>185850</t>
+          <t>252484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277877</t>
+          <t>322818</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>257592</t>
+          <t>292380</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>212886</t>
+          <t>265357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289061</t>
+          <t>322489</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>500402</t>
+          <t>576299</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>425593</t>
+          <t>531576</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>544610</t>
+          <t>623814</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>84747</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63662</t>
+          <t>81209</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108011</t>
+          <t>123496</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>311414</t>
+          <t>124418</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>104611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>939873</t>
+          <t>142689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>396161</t>
+          <t>224819</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>188971</t>
+          <t>199758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>982698</t>
+          <t>255958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>77624</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>63424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3444873</t>
+          <t>3511745</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3444873</t>
+          <t>3511745</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3444873</t>
+          <t>3511745</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3644564</t>
+          <t>3718089</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3644564</t>
+          <t>3718089</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3644564</t>
+          <t>3718089</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7089438</t>
+          <t>7229833</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7089438</t>
+          <t>7229833</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7089438</t>
+          <t>7229833</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
